--- a/services/sim/lms/users_data.xlsx
+++ b/services/sim/lms/users_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="42">
   <si>
     <t>userCode</t>
   </si>
@@ -73,10 +73,7 @@
     <t>test1</t>
   </si>
   <si>
-    <t>123123123</t>
-  </si>
-  <si>
-    <t>123123</t>
+    <t>Hsyc@2025</t>
   </si>
   <si>
     <t>123456</t>
@@ -109,7 +106,7 @@
     <t>79957648</t>
   </si>
   <si>
-    <t>04234412</t>
+    <t>4234412</t>
   </si>
   <si>
     <t>省物流处</t>
@@ -558,37 +555,37 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>27</v>
       </c>
-      <c r="F2" t="s">
-        <v>28</v>
-      </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" t="s">
         <v>34</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>35</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>36</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>37</v>
-      </c>
-      <c r="N2" t="s">
-        <v>38</v>
       </c>
       <c r="O2" t="s">
         <v>15</v>
@@ -602,34 +599,34 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
         <v>26</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" t="s">
         <v>27</v>
       </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
         <v>35</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>36</v>
       </c>
-      <c r="M3" t="s">
-        <v>37</v>
-      </c>
       <c r="N3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O3" t="s">
         <v>15</v>
@@ -640,40 +637,40 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
         <v>26</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" t="s">
         <v>35</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>36</v>
       </c>
-      <c r="M4" t="s">
-        <v>37</v>
-      </c>
       <c r="N4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -681,40 +678,40 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>26</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
         <v>27</v>
       </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" t="s">
         <v>35</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>36</v>
       </c>
-      <c r="M5" t="s">
-        <v>37</v>
-      </c>
       <c r="N5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" t="s">
         <v>41</v>
-      </c>
-      <c r="O5" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
